--- a/PsychoPy/Pics_all.xlsx
+++ b/PsychoPy/Pics_all.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iowa-my.sharepoint.com/personal/markberardi_uiowa_edu/Documents/Documents/GitHub/VLT_LITE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iowa-my.sharepoint.com/personal/markberardi_uiowa_edu/Documents/Documents/GitHub/VLT-VBAL/PsychoPy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="11_F25DC773A252ABDACC104808B19977C25BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6A2E145-5D5C-4370-87AE-117C1478F943}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="11_F25DC773A252ABDACC104808B19977C25BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3327300-4B5B-4A97-85CE-05D2CEC1B10E}"/>
   <bookViews>
-    <workbookView xWindow="20160" yWindow="9030" windowWidth="10545" windowHeight="10635" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,54 +36,144 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>picture_image</t>
   </si>
   <si>
-    <t>Pics/Frog01.png</t>
-  </si>
-  <si>
-    <t>Pics/Frog02.png</t>
-  </si>
-  <si>
-    <t>Pics/Frog03.png</t>
-  </si>
-  <si>
-    <t>Pics/Frog04.png</t>
-  </si>
-  <si>
-    <t>Pics/Frog05.png</t>
-  </si>
-  <si>
-    <t>Pics/Frog06.png</t>
-  </si>
-  <si>
-    <t>Pics/Frog07.png</t>
-  </si>
-  <si>
-    <t>Pics/Frog08.png</t>
-  </si>
-  <si>
-    <t>Pics/Frog09.png</t>
-  </si>
-  <si>
-    <t>Pics/Frog10.png</t>
-  </si>
-  <si>
-    <t>Pics/Frog11.png</t>
-  </si>
-  <si>
-    <t>Pics/Frog12.png</t>
-  </si>
-  <si>
-    <t>Pics/Frog13.png</t>
-  </si>
-  <si>
-    <t>Pics/Frog14.png</t>
-  </si>
-  <si>
-    <t>Pics/Frog15.png</t>
+    <t>Pics/FrogA01.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogA02.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogA03.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogA04.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogA05.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogA06.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogA07.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogA08.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogA09.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogA10.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogA11.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogA12.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogA13.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogA14.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogA15.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogB01.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogB02.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogB03.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogB04.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogB05.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogB06.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogB07.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogB08.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogB09.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogB10.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogB11.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogB12.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogB13.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogB14.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogB15.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogC01.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogC02.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogC03.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogC04.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogC05.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogC06.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogC07.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogC08.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogC09.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogC10.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogC11.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogC12.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogC13.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogC14.png</t>
+  </si>
+  <si>
+    <t>Pics/FrogC15.png</t>
   </si>
 </sst>
 </file>
@@ -401,87 +491,237 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A46"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
